--- a/grupos/3APV - Estadisticos 20231.xlsx
+++ b/grupos/3APV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -170,12 +170,12 @@
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
@@ -206,30 +206,24 @@
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>SOTO</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
     <t>IGNACIO</t>
   </si>
   <si>
@@ -239,13 +233,10 @@
     <t>JOSE</t>
   </si>
   <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
     <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
   </si>
 </sst>
 </file>
@@ -756,19 +747,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -833,19 +824,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -872,16 +863,16 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -910,19 +901,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -949,16 +940,16 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -987,19 +978,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1026,10 +1017,10 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1064,19 +1055,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1100,13 +1091,13 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>10</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1141,19 +1132,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1218,19 +1209,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1295,19 +1286,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1372,19 +1363,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1408,7 +1399,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1449,19 +1440,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1526,19 +1517,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1562,7 +1553,7 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1603,19 +1594,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1642,7 +1633,7 @@
         <v>5</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1680,19 +1671,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1722,7 +1713,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -1757,19 +1748,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1793,13 +1784,13 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -1834,19 +1825,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1870,10 +1861,10 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -1911,19 +1902,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1953,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -1988,19 +1979,19 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2024,19 +2015,19 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2065,19 +2056,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2104,7 +2095,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2142,19 +2133,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2184,7 +2175,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2219,19 +2210,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2258,16 +2249,16 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2296,19 +2287,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2335,10 +2326,10 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2373,19 +2364,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2409,13 +2400,13 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2450,19 +2441,19 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2486,19 +2477,19 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2515,7 +2506,7 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2527,7 +2518,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2556,19 +2547,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2592,13 +2583,13 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>10</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -2743,37 +2734,37 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="J4">
-        <v>53.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K4">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>80</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="P4">
-        <v>53.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>80</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2802,37 +2793,37 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J5">
-        <v>63.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P5">
-        <v>63.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2864,16 +2855,16 @@
         <v>95.59999999999999</v>
       </c>
       <c r="J6">
-        <v>56.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K6">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="L6">
         <v>100</v>
       </c>
       <c r="M6">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -2882,16 +2873,16 @@
         <v>95.59999999999999</v>
       </c>
       <c r="P6">
-        <v>56.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q6">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="R6">
         <v>100</v>
       </c>
       <c r="S6">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2923,16 +2914,16 @@
         <v>91.09999999999999</v>
       </c>
       <c r="J7">
-        <v>56.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="N7">
         <v>100</v>
@@ -2941,16 +2932,16 @@
         <v>91.09999999999999</v>
       </c>
       <c r="P7">
-        <v>56.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="R7">
         <v>100</v>
       </c>
       <c r="S7">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2979,37 +2970,37 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J8">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P8">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3038,10 +3029,10 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="J9">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3050,16 +3041,16 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="P9">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3068,7 +3059,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3097,13 +3088,13 @@
         <v>95</v>
       </c>
       <c r="I10">
-        <v>91.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="J10">
-        <v>56.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K10">
-        <v>95.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L10">
         <v>93.8</v>
@@ -3115,13 +3106,13 @@
         <v>95</v>
       </c>
       <c r="O10">
-        <v>91.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="P10">
-        <v>56.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q10">
-        <v>95.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R10">
         <v>93.8</v>
@@ -3156,10 +3147,10 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>95.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J11">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3168,16 +3159,16 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11">
-        <v>95.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P11">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3186,7 +3177,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3215,37 +3206,37 @@
         <v>95</v>
       </c>
       <c r="I12">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J12">
-        <v>56.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K12">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="L12">
         <v>81.3</v>
       </c>
       <c r="M12">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="N12">
         <v>95</v>
       </c>
       <c r="O12">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="P12">
-        <v>56.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q12">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="R12">
         <v>81.3</v>
       </c>
       <c r="S12">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3277,7 +3268,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3286,7 +3277,7 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -3295,7 +3286,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3304,7 +3295,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3333,10 +3324,10 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="J14">
-        <v>66.7</v>
+        <v>97.7</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -3345,16 +3336,16 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="P14">
-        <v>66.7</v>
+        <v>97.7</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3363,7 +3354,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3392,37 +3383,37 @@
         <v>92.5</v>
       </c>
       <c r="I15">
-        <v>88.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="J15">
-        <v>56.7</v>
+        <v>79.5</v>
       </c>
       <c r="K15">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="L15">
         <v>81.3</v>
       </c>
       <c r="M15">
-        <v>60</v>
+        <v>61.4</v>
       </c>
       <c r="N15">
         <v>92.5</v>
       </c>
       <c r="O15">
-        <v>88.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="P15">
-        <v>56.7</v>
+        <v>79.5</v>
       </c>
       <c r="Q15">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="R15">
         <v>81.3</v>
       </c>
       <c r="S15">
-        <v>60</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3451,10 +3442,10 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -3463,16 +3454,16 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -3481,7 +3472,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3513,16 +3504,16 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>56.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K17">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>68</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="N17">
         <v>97.5</v>
@@ -3531,16 +3522,16 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>56.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q17">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>68</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3569,37 +3560,37 @@
         <v>97.5</v>
       </c>
       <c r="I18">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J18">
-        <v>56.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K18">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>68</v>
+        <v>77.3</v>
       </c>
       <c r="N18">
         <v>97.5</v>
       </c>
       <c r="O18">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P18">
-        <v>56.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q18">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>68</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3631,7 +3622,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -3640,7 +3631,7 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -3649,7 +3640,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -3658,7 +3649,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3687,10 +3678,10 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>97.8</v>
+        <v>96.7</v>
       </c>
       <c r="J20">
-        <v>60</v>
+        <v>93.2</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -3699,16 +3690,16 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N20">
         <v>100</v>
       </c>
       <c r="O20">
-        <v>97.8</v>
+        <v>96.7</v>
       </c>
       <c r="P20">
-        <v>60</v>
+        <v>93.2</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -3717,7 +3708,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3746,10 +3737,10 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J21">
-        <v>66.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -3758,16 +3749,16 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>80</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="N21">
         <v>100</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P21">
-        <v>66.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -3776,7 +3767,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>80</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3805,37 +3796,37 @@
         <v>95</v>
       </c>
       <c r="I22">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J22">
-        <v>56.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K22">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="L22">
         <v>87.5</v>
       </c>
       <c r="M22">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N22">
         <v>95</v>
       </c>
       <c r="O22">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P22">
-        <v>56.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Q22">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="R22">
         <v>87.5</v>
       </c>
       <c r="S22">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3864,37 +3855,37 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="J23">
-        <v>56.7</v>
+        <v>93.2</v>
       </c>
       <c r="K23">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N23">
         <v>100</v>
       </c>
       <c r="O23">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="P23">
-        <v>56.7</v>
+        <v>93.2</v>
       </c>
       <c r="Q23">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3926,7 +3917,7 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>66.7</v>
+        <v>93.2</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -3935,7 +3926,7 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N24">
         <v>100</v>
@@ -3944,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>66.7</v>
+        <v>93.2</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -3953,7 +3944,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3982,37 +3973,37 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J25">
-        <v>63.3</v>
+        <v>93.2</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
-        <v>80</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="N25">
         <v>100</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P25">
-        <v>63.3</v>
+        <v>93.2</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>80</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4044,16 +4035,16 @@
         <v>95.59999999999999</v>
       </c>
       <c r="J26">
-        <v>63.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K26">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -4062,16 +4053,16 @@
         <v>95.59999999999999</v>
       </c>
       <c r="P26">
-        <v>63.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q26">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4126,7 +4117,7 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -4135,7 +4126,7 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -4144,7 +4135,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -4153,7 +4144,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4242,7 +4233,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4263,7 +4254,7 @@
         <v>20.8</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4274,7 +4265,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -4283,19 +4274,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>79.2</v>
+        <v>83.3</v>
       </c>
       <c r="G4" s="2">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4315,19 +4306,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4441,7 +4432,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4479,16 +4470,16 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4502,10 +4493,10 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4528,13 +4519,13 @@
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4551,7 +4542,7 @@
         <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4571,16 +4562,16 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4594,10 +4585,10 @@
         <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4611,22 +4602,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920286</v>
+        <v>22330051920277</v>
       </c>
       <c r="B8" t="s">
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4637,67 +4628,21 @@
         <v>22330051920286</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
         <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920272</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920277</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20231.xlsx
+++ b/grupos/3APV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="75">
   <si>
     <t>Materia</t>
   </si>
@@ -167,12 +167,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
@@ -206,6 +206,9 @@
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -231,6 +234,9 @@
   </si>
   <si>
     <t>JOSE</t>
+  </si>
+  <si>
+    <t>ERIK</t>
   </si>
   <si>
     <t>OSCAR</t>
@@ -756,7 +762,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -833,7 +839,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -869,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -910,7 +916,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -987,7 +993,7 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1023,7 +1029,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1064,7 +1070,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -1100,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1141,7 +1147,7 @@
         <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -1218,7 +1224,7 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>3</v>
@@ -1295,7 +1301,7 @@
         <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -1331,7 +1337,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1372,7 +1378,7 @@
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -1408,7 +1414,7 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1449,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -1485,7 +1491,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1526,7 +1532,7 @@
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1562,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1603,7 +1609,7 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>3</v>
@@ -1639,7 +1645,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1680,7 +1686,7 @@
         <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>7</v>
@@ -1716,7 +1722,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1757,7 +1763,7 @@
         <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -1793,7 +1799,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1834,7 +1840,7 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M18">
         <v>3</v>
@@ -1870,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1911,7 +1917,7 @@
         <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -1988,7 +1994,7 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -2024,7 +2030,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2065,7 +2071,7 @@
         <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>7</v>
@@ -2142,7 +2148,7 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -2219,7 +2225,7 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2296,7 +2302,7 @@
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>7</v>
@@ -2373,7 +2379,7 @@
         <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>7</v>
@@ -2450,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>7</v>
@@ -2556,7 +2562,7 @@
         <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>8</v>
@@ -2592,7 +2598,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2743,7 +2749,7 @@
         <v>95.7</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M4">
         <v>84.09999999999999</v>
@@ -2761,7 +2767,7 @@
         <v>95.7</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S4">
         <v>84.09999999999999</v>
@@ -2802,7 +2808,7 @@
         <v>97.8</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M5">
         <v>90.90000000000001</v>
@@ -2820,7 +2826,7 @@
         <v>97.8</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S5">
         <v>90.90000000000001</v>
@@ -2861,7 +2867,7 @@
         <v>97.8</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M6">
         <v>88.59999999999999</v>
@@ -2879,7 +2885,7 @@
         <v>97.8</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S6">
         <v>88.59999999999999</v>
@@ -2920,7 +2926,7 @@
         <v>97.8</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M7">
         <v>75</v>
@@ -2938,7 +2944,7 @@
         <v>97.8</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S7">
         <v>75</v>
@@ -3097,7 +3103,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="L10">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -3115,7 +3121,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="R10">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3215,7 +3221,7 @@
         <v>93.5</v>
       </c>
       <c r="L12">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="M12">
         <v>50</v>
@@ -3233,7 +3239,7 @@
         <v>93.5</v>
       </c>
       <c r="R12">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="S12">
         <v>50</v>
@@ -3392,7 +3398,7 @@
         <v>93.5</v>
       </c>
       <c r="L15">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M15">
         <v>61.4</v>
@@ -3410,7 +3416,7 @@
         <v>93.5</v>
       </c>
       <c r="R15">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="S15">
         <v>61.4</v>
@@ -3569,7 +3575,7 @@
         <v>95.7</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M18">
         <v>77.3</v>
@@ -3587,7 +3593,7 @@
         <v>95.7</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S18">
         <v>77.3</v>
@@ -3805,7 +3811,7 @@
         <v>95.7</v>
       </c>
       <c r="L22">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M22">
         <v>88.59999999999999</v>
@@ -3823,7 +3829,7 @@
         <v>95.7</v>
       </c>
       <c r="R22">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S22">
         <v>88.59999999999999</v>
@@ -4201,7 +4207,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -4210,19 +4216,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>75</v>
+        <v>70.8</v>
       </c>
       <c r="G2" s="2">
-        <v>25</v>
+        <v>29.2</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4233,7 +4239,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4242,19 +4248,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>79.2</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2">
-        <v>20.8</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4432,7 +4438,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4470,16 +4476,16 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4493,16 +4499,16 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4519,7 +4525,7 @@
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4542,13 +4548,13 @@
         <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4562,10 +4568,10 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4585,16 +4591,16 @@
         <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4602,22 +4608,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920277</v>
+        <v>22330051920276</v>
       </c>
       <c r="B8" t="s">
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4625,7 +4631,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920286</v>
+        <v>22330051920277</v>
       </c>
       <c r="B9" t="s">
         <v>63</v>
@@ -4634,15 +4640,38 @@
         <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920286</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20231.xlsx
+++ b/grupos/3APV - Estadisticos 20231.xlsx
@@ -179,10 +179,10 @@
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
+  </si>
+  <si>
     <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
     <t>NC</t>
@@ -750,7 +750,7 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -786,7 +786,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -827,7 +827,7 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>9</v>
@@ -904,7 +904,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -981,7 +981,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -1058,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>9</v>
@@ -1135,7 +1135,7 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -1212,7 +1212,7 @@
         <v>4</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -1289,7 +1289,7 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -1366,7 +1366,7 @@
         <v>3</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -1443,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -1520,7 +1520,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>9</v>
@@ -1556,7 +1556,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1597,7 +1597,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>5</v>
@@ -1633,7 +1633,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>5</v>
@@ -1674,7 +1674,7 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
         <v>8</v>
@@ -1751,7 +1751,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>9</v>
@@ -1828,7 +1828,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -1905,7 +1905,7 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -1982,7 +1982,7 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -2136,7 +2136,7 @@
         <v>4</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -2172,7 +2172,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2213,7 +2213,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -2290,7 +2290,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>7</v>
@@ -2367,7 +2367,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>8</v>
@@ -2403,7 +2403,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2444,7 +2444,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
         <v>7</v>
@@ -2509,7 +2509,7 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>8</v>
@@ -2550,7 +2550,7 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -2586,7 +2586,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>9</v>
@@ -2737,7 +2737,7 @@
         <v>80</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I4">
         <v>90</v>
@@ -2755,7 +2755,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O4">
         <v>90</v>
@@ -2914,7 +2914,7 @@
         <v>68</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I7">
         <v>91.09999999999999</v>
@@ -2932,7 +2932,7 @@
         <v>75</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O7">
         <v>91.09999999999999</v>
@@ -3091,7 +3091,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="I10">
         <v>90</v>
@@ -3109,7 +3109,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="O10">
         <v>90</v>
@@ -3386,7 +3386,7 @@
         <v>60</v>
       </c>
       <c r="H15">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="I15">
         <v>80</v>
@@ -3404,7 +3404,7 @@
         <v>61.4</v>
       </c>
       <c r="N15">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="O15">
         <v>80</v>
@@ -3563,7 +3563,7 @@
         <v>68</v>
       </c>
       <c r="H18">
-        <v>97.5</v>
+        <v>96.3</v>
       </c>
       <c r="I18">
         <v>94.40000000000001</v>
@@ -3581,7 +3581,7 @@
         <v>77.3</v>
       </c>
       <c r="N18">
-        <v>97.5</v>
+        <v>96.3</v>
       </c>
       <c r="O18">
         <v>94.40000000000001</v>
@@ -3740,7 +3740,7 @@
         <v>80</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I21">
         <v>97.8</v>
@@ -3758,7 +3758,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="O21">
         <v>97.8</v>
@@ -3976,7 +3976,7 @@
         <v>80</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I25">
         <v>97.8</v>
@@ -3994,7 +3994,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="O25">
         <v>97.8</v>
@@ -4335,28 +4335,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>24</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4367,16 +4367,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3APV - Estadisticos 20231.xlsx
+++ b/grupos/3APV - Estadisticos 20231.xlsx
@@ -3206,7 +3206,7 @@
         <v>81.3</v>
       </c>
       <c r="G12">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H12">
         <v>95</v>
@@ -3224,7 +3224,7 @@
         <v>87.5</v>
       </c>
       <c r="M12">
-        <v>50</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N12">
         <v>95</v>
@@ -3242,7 +3242,7 @@
         <v>87.5</v>
       </c>
       <c r="S12">
-        <v>50</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:19">

--- a/grupos/3APV - Estadisticos 20231.xlsx
+++ b/grupos/3APV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="72">
   <si>
     <t>Materia</t>
   </si>
@@ -71,7 +71,7 @@
     <t>CRUZ GARCIA ANA KAREN</t>
   </si>
   <si>
-    <t>GARCIA ------ CARLOS DAVID</t>
+    <t>GARCIA ALONSO CARLOS DAVID</t>
   </si>
   <si>
     <t>GONZALEZ CASASOLA SERGIO IVAN</t>
@@ -176,15 +176,15 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -203,9 +203,6 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -218,9 +215,6 @@
     <t>SOTO</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
@@ -231,9 +225,6 @@
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
   </si>
   <si>
     <t>ERIK</t>
@@ -768,28 +759,28 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -845,22 +836,22 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -872,13 +863,13 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -922,22 +913,22 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -949,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -999,28 +990,28 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>8</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1076,28 +1067,28 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1153,22 +1144,22 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1186,7 +1177,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1230,25 +1221,25 @@
         <v>3</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1307,22 +1298,22 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1340,7 +1331,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1384,34 +1375,34 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1461,22 +1452,22 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1538,22 +1529,22 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1615,34 +1606,34 @@
         <v>3</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>5</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1692,22 +1683,22 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1719,13 +1710,13 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1769,34 +1760,34 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>9</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -1846,28 +1837,28 @@
         <v>3</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -1923,22 +1914,22 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2000,22 +1991,22 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2077,22 +2068,22 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2154,34 +2145,34 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>7</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2231,22 +2222,22 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2308,34 +2299,34 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>9</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2385,25 +2376,25 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2418,7 +2409,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2462,22 +2453,22 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2489,7 +2480,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2515,10 +2506,10 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2568,34 +2559,34 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>8</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>10</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2755,22 +2746,22 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N4">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P4">
-        <v>86.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q4">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="R4">
         <v>90.59999999999999</v>
       </c>
       <c r="S4">
-        <v>84.09999999999999</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2817,19 +2808,19 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>97.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P5">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="R5">
         <v>93.8</v>
       </c>
       <c r="S5">
-        <v>90.90000000000001</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2873,22 +2864,22 @@
         <v>88.59999999999999</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O6">
-        <v>95.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="P6">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q6">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="R6">
         <v>93.8</v>
       </c>
       <c r="S6">
-        <v>88.59999999999999</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2932,22 +2923,22 @@
         <v>75</v>
       </c>
       <c r="N7">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O7">
-        <v>91.09999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="P7">
-        <v>84.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q7">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="R7">
         <v>90.59999999999999</v>
       </c>
       <c r="S7">
-        <v>75</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2991,22 +2982,22 @@
         <v>88.59999999999999</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O8">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>88.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3050,10 +3041,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O9">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3065,7 +3056,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>90.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3109,22 +3100,22 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>92.5</v>
+        <v>58.6</v>
       </c>
       <c r="O10">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="P10">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="Q10">
-        <v>89.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="R10">
         <v>90.59999999999999</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3168,10 +3159,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O11">
-        <v>92.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3183,7 +3174,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>90.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3227,22 +3218,22 @@
         <v>86.40000000000001</v>
       </c>
       <c r="N12">
-        <v>95</v>
+        <v>94.5</v>
       </c>
       <c r="O12">
-        <v>96.7</v>
+        <v>96.5</v>
       </c>
       <c r="P12">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q12">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R12">
         <v>87.5</v>
       </c>
       <c r="S12">
-        <v>86.40000000000001</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3301,7 +3292,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3348,10 +3339,10 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>97.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P14">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3360,7 +3351,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>88.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3404,22 +3395,22 @@
         <v>61.4</v>
       </c>
       <c r="N15">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O15">
-        <v>80</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="P15">
-        <v>79.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q15">
-        <v>93.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="R15">
         <v>71.90000000000001</v>
       </c>
       <c r="S15">
-        <v>61.4</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3466,19 +3457,19 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>97.8</v>
+        <v>97.2</v>
       </c>
       <c r="P16">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="R16">
         <v>100</v>
       </c>
       <c r="S16">
-        <v>90.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3522,22 +3513,22 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N17">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="P17">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q17">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>84.09999999999999</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3581,22 +3572,22 @@
         <v>77.3</v>
       </c>
       <c r="N18">
-        <v>96.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="O18">
-        <v>94.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="P18">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q18">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R18">
         <v>90.59999999999999</v>
       </c>
       <c r="S18">
-        <v>77.3</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3655,7 +3646,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>90.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3699,13 +3690,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O20">
-        <v>96.7</v>
+        <v>97.2</v>
       </c>
       <c r="P20">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -3714,7 +3705,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>90.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3758,22 +3749,22 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N21">
-        <v>98.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O21">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P21">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>84.09999999999999</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3817,22 +3808,22 @@
         <v>88.59999999999999</v>
       </c>
       <c r="N22">
-        <v>95</v>
+        <v>94.5</v>
       </c>
       <c r="O22">
-        <v>94.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="P22">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q22">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="R22">
         <v>90.59999999999999</v>
       </c>
       <c r="S22">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3879,19 +3870,19 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>97.8</v>
+        <v>97.2</v>
       </c>
       <c r="P23">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q23">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3938,10 +3929,10 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P24">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -3950,7 +3941,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>88.59999999999999</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3994,22 +3985,22 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N25">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="O25">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P25">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="Q25">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>84.09999999999999</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4056,19 +4047,19 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>95.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="P26">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q26">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>90.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4091,7 +4082,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4150,7 +4141,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4260,7 +4251,7 @@
         <v>25</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4280,16 +4271,16 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="G4" s="2">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -4303,7 +4294,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
@@ -4324,7 +4315,7 @@
         <v>12</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4335,28 +4326,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4367,16 +4358,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4388,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4438,7 +4429,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4476,10 +4467,10 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -4499,10 +4490,10 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4525,13 +4516,13 @@
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4539,22 +4530,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920405</v>
+        <v>22330051920276</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4562,22 +4553,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920273</v>
+        <v>22330051920277</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4585,10 +4576,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920273</v>
+        <v>22330051920286</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -4597,81 +4588,12 @@
         <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920276</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920277</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920286</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20231.xlsx
+++ b/grupos/3APV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="67">
   <si>
     <t>Materia</t>
   </si>
@@ -167,18 +167,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
@@ -197,43 +197,28 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
+    <t>JOSE</t>
   </si>
   <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>HECTOR MISAEL</t>
   </si>
   <si>
     <t>IGNACIO</t>
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
   </si>
 </sst>
 </file>
@@ -771,7 +756,7 @@
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>7</v>
@@ -789,7 +774,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -848,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>7</v>
@@ -866,7 +851,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -925,7 +910,7 @@
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -943,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1002,7 +987,7 @@
         <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>7</v>
@@ -1020,7 +1005,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1079,7 +1064,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>10</v>
@@ -1097,7 +1082,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1156,7 +1141,7 @@
         <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>6</v>
@@ -1233,7 +1218,7 @@
         <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>3</v>
@@ -1310,7 +1295,7 @@
         <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>6</v>
@@ -1387,7 +1372,7 @@
         <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>3</v>
@@ -1405,7 +1390,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1464,7 +1449,7 @@
         <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>10</v>
@@ -1541,7 +1526,7 @@
         <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -1618,7 +1603,7 @@
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>5</v>
@@ -1695,7 +1680,7 @@
         <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>9</v>
@@ -1713,7 +1698,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1772,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>8</v>
@@ -1790,7 +1775,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1849,7 +1834,7 @@
         <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>5</v>
@@ -1867,7 +1852,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1926,7 +1911,7 @@
         <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>10</v>
@@ -1944,7 +1929,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2003,7 +1988,7 @@
         <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -2021,7 +2006,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2080,7 +2065,7 @@
         <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -2098,7 +2083,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2157,7 +2142,7 @@
         <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>5</v>
@@ -2175,7 +2160,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2234,7 +2219,7 @@
         <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>7</v>
@@ -2252,7 +2237,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2311,7 +2296,7 @@
         <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -2388,7 +2373,7 @@
         <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>5</v>
@@ -2465,7 +2450,7 @@
         <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>7</v>
@@ -2483,7 +2468,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2571,7 +2556,7 @@
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>10</v>
@@ -2758,7 +2743,7 @@
         <v>97</v>
       </c>
       <c r="R4">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="S4">
         <v>95.3</v>
@@ -2817,7 +2802,7 @@
         <v>98.5</v>
       </c>
       <c r="R5">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="S5">
         <v>96.90000000000001</v>
@@ -2876,7 +2861,7 @@
         <v>98.5</v>
       </c>
       <c r="R6">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="S6">
         <v>95.3</v>
@@ -2935,7 +2920,7 @@
         <v>97</v>
       </c>
       <c r="R7">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="S7">
         <v>85.90000000000001</v>
@@ -3112,7 +3097,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="R10">
-        <v>90.59999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="S10">
         <v>71.90000000000001</v>
@@ -3230,7 +3215,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="R12">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="S12">
         <v>82.8</v>
@@ -3407,7 +3392,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="R15">
-        <v>71.90000000000001</v>
+        <v>56.3</v>
       </c>
       <c r="S15">
         <v>67.2</v>
@@ -3584,7 +3569,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="R18">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="S18">
         <v>78.09999999999999</v>
@@ -3820,7 +3805,7 @@
         <v>95.5</v>
       </c>
       <c r="R22">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="S22">
         <v>89.09999999999999</v>
@@ -4198,7 +4183,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -4207,19 +4192,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>70.8</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2">
-        <v>29.2</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4230,7 +4215,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4239,19 +4224,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="G3" s="2">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4262,28 +4247,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="G4" s="2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4294,28 +4279,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>22</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="G5" s="2">
-        <v>12</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4429,7 +4414,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4461,22 +4446,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920396</v>
+        <v>22330051920279</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
       </c>
       <c r="C2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4484,22 +4469,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920396</v>
+        <v>22330051920279</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
         <v>64</v>
       </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4507,22 +4492,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920405</v>
+        <v>21330051920396</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4530,70 +4515,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920276</v>
+        <v>22330051920405</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>49</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920277</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920286</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20231.xlsx
+++ b/grupos/3APV - Estadisticos 20231.xlsx
@@ -762,19 +762,19 @@
         <v>7</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -842,19 +842,19 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -916,22 +916,22 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -993,22 +993,22 @@
         <v>7</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1070,10 +1070,10 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1082,10 +1082,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1147,22 +1147,22 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>10</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1230,7 +1230,7 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1301,22 +1301,22 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>10</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1378,19 +1378,19 @@
         <v>3</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1458,7 +1458,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1467,10 +1467,10 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1535,7 +1535,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1544,10 +1544,10 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1615,10 +1615,10 @@
         <v>5</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1689,19 +1689,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1763,22 +1763,22 @@
         <v>8</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1843,16 +1843,16 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>5</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1917,22 +1917,22 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1994,22 +1994,22 @@
         <v>6</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2074,19 +2074,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2148,19 +2148,19 @@
         <v>5</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>5</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2225,22 +2225,22 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2302,22 +2302,22 @@
         <v>9</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2379,22 +2379,22 @@
         <v>5</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2459,19 +2459,19 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2500,7 +2500,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2562,22 +2562,22 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>10</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4204,7 +4204,7 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4236,7 +4236,7 @@
         <v>12.5</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4268,7 +4268,7 @@
         <v>12</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4300,7 +4300,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4332,7 +4332,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3APV - Estadisticos 20231.xlsx
+++ b/grupos/3APV - Estadisticos 20231.xlsx
@@ -762,19 +762,19 @@
         <v>7</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -842,19 +842,19 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -916,22 +916,22 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -993,22 +993,22 @@
         <v>7</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1070,10 +1070,10 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1082,10 +1082,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1147,22 +1147,22 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>10</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1230,7 +1230,7 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1301,22 +1301,22 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>10</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1378,19 +1378,19 @@
         <v>3</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1458,7 +1458,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1467,10 +1467,10 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1535,7 +1535,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1544,10 +1544,10 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1615,10 +1615,10 @@
         <v>5</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1689,19 +1689,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>10</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1763,22 +1763,22 @@
         <v>8</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1843,16 +1843,16 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>5</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1917,22 +1917,22 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>10</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1994,22 +1994,22 @@
         <v>6</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2074,19 +2074,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2148,19 +2148,19 @@
         <v>5</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>5</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2225,22 +2225,22 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2302,22 +2302,22 @@
         <v>9</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2379,22 +2379,22 @@
         <v>5</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2459,19 +2459,19 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2500,7 +2500,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2562,22 +2562,22 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>10</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4204,7 +4204,7 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4236,7 +4236,7 @@
         <v>12.5</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4268,7 +4268,7 @@
         <v>12</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4300,7 +4300,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4332,7 +4332,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
